--- a/docs/user-research/questionnaires/cleaned/contact_list.xlsx
+++ b/docs/user-research/questionnaires/cleaned/contact_list.xlsx
@@ -413,8 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="50" customWidth="1" min="25" max="25"/>
+    <col width="50" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -429,7 +459,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CEIBS校友</t>
+          <t>CEIBS</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -454,37 +484,107 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>当前状态(Q1)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>尝试历史</t>
+          <t>尝试历史(Q2)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>失控频率</t>
+          <t>失控频率(Q6)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>失控后反应</t>
+          <t>失控后反应(Q7)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>偏好方式</t>
+          <t>偏好方式(Q8)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>过去一年花费</t>
+          <t>花费(Q11)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>一句话感受</t>
+          <t>干扰-工作压力</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>干扰-社交饮食</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>干扰-外出离家</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>干扰-情绪波动</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>支持-靠自己</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>支持-家人朋友</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>支持-线上社群</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>支持-私教一对一</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>支持-社交打卡</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>使用工具(Q10)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>私教有效原因(Q9b)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>具体失控经历(Q12)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>坚持最久方法(Q13)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>一句话感受(Q14)</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>联系建议</t>
         </is>
       </c>
     </row>
@@ -541,7 +641,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>难以恢复——会低落一阵子，或者中断后很难重新捡起来</t>
+          <t>难以恢复——会低落一阵子，或者</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -556,14 +656,64 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>(空)</t>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>高痛感用户，当前未行动。切入点：不要催促重启，而是了解当前状态和顾虑。 | 失控后难以恢复，可探讨恢复过程中最困难的部分。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 私教体验正面，可聊为什么有帮助、为什么没继续。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>C010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -578,12 +728,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>18721691082</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>不愿透露</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -608,39 +758,99 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>很少</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>难以恢复——会低落一阵子，或者中断后很难重新捡起来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>公开做，社交监督对自己有用</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>一万以上</t>
+          <t>三千到一万</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>减肥药是伟大的发明</t>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋H.其他（请填写）</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>各种都试过了，用过替尔泊肽和司美格鲁肽减重版（可能体质原因 一斤都没瘦 食欲也贼好）；用过日本的什么燃脂片也没用。</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>反正发现还是管住嘴迈开腿最管用</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>核心目标用户。多次尝试说明动机强但缺乏持续支持，聊天切入点：过去哪些方法坚持最久、为什么停了。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 一句话感受可作为开场共鸣点：'反正发现还是管住嘴迈开腿最管用' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C009</t>
+          <t>C011</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>起步行动者</t>
+          <t>轻度脱轨</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,7 +860,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Xhc92894</t>
+          <t>15951002536</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -670,27 +880,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>是的，我现在正在做</t>
+          <t>断断续续地在做，时有时无</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3年以上，1-5次</t>
+          <t>不到1年，1-2次</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>很少</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>几乎没影响——不太在意，很快就过去了</t>
+          <t>当天放大——"既然已经破功了，</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -700,19 +910,84 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>瘦下的你永远不想胖回去，对自己狠一点，人的能量是无限的。</t>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>D.私教或营养师（线上或线下）┋E.付费课程或训练营</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>晚上因为工作，没有吃晚饭，然后夜宵吃了一份炸鸡</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>练拳，因为我喜欢练拳，一直有习惯，但是因为工作就没有练了</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>当有比控制体重更重要的事情，体重就不可能控制</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>痛感较低，社交偏好较高。需确认是否真的对私密 AI 教练有兴趣。 | 有当天放大模式，可聊'破功后当天'的典型心理过程。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 有具体失控经历可展开：'晚上因为工作，没有吃晚饭，然后夜宵吃了一份炸鸡...' | 一句话感受可作为开场共鸣点：'当有比控制体重更重要的事情，体重就不可能控制'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>C014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>反复行动者</t>
+          <t>起步行动者</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -722,12 +997,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18721691082</t>
+          <t>17621520001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -737,7 +1012,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>节奏比较固定，大部分时间能自己安排（比如远程办公、自由职业、独立创作）</t>
+          <t>目前不在工作（学生、全职家庭、待业等）</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -747,44 +1022,94 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1-3年，3-5次</t>
+          <t>1-3年，1-2次</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>时不时会有（一周1-2次）</t>
+          <t>很少</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>三千到一万</t>
+          <t>数百元</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>反正发现还是管住嘴迈开腿最管用</t>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>C.智能硬件（体重秤、手环、手表等）</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>刚起步，困难度较低。切入点：了解当前在用什么方法、遇到的第一个卡点是什么。 | 工作压力是主要干扰源，可从工作节奏切入。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C011</t>
+          <t>C018</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>轻度脱轨</t>
+          <t>重度脱轨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -794,22 +1119,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15951002536</t>
+          <t>13918155081</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25-30岁</t>
+          <t>41岁以上</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
+          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -819,7 +1144,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>不到1年，1-2次</t>
+          <t>1-3年，3-5次</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -829,34 +1154,99 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>当天放大——"既然已经破功了，今天就算了"，当天彻底放开</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>希望有人支持，但想私密地进行</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>没花过钱</t>
+          <t>数百元</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>当有比控制体重更重要的事情，体重就不可能控制</t>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>C.智能硬件（体重秤、手环、手表等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>加班太晚没吃，回家10点了，也不饿了，心里也感觉不该吃了，但想想这么辛苦，忍不住反而吃了好多</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>几个人一起</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>从未停止，从未成功</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>高痛感用户，当前未行动。切入点：不要催促重启，而是了解当前状态和顾虑。 | 工作压力是主要干扰源，可从工作节奏切入。 | 有具体失控经历可展开：'加班太晚没吃，回家10点了，也不饿了，心里也感觉不该吃了，但...' | 一句话感受可作为开场共鸣点：'从未停止，从未成功'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C014</t>
+          <t>C020</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>起步行动者</t>
+          <t>反复行动者</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -866,22 +1256,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17621520001</t>
+          <t>cincin_mei</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25-30岁</t>
+          <t>31-40岁</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>目前不在工作（学生、全职家庭、待业等）</t>
+          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -891,44 +1281,109 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1-3年，1-2次</t>
+          <t>3年以上，6次以上（反复重启）</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>很少</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>几乎没影响——不太在意，很快就</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>数百元</t>
+          <t>三千到一万</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>(空)</t>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>C.智能硬件（体重秤、手环、手表等）┋D.私教或营养师（线上或线下）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>暴饮暴食，买一堆零食吃，喝酒</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>去健身房</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>很难减，没有正反馈就很容易放弃</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>核心目标用户。多次尝试说明动机强但缺乏持续支持，聊天切入点：过去哪些方法坚持最久、为什么停了。 | 工作压力是主要干扰源，可从工作节奏切入。 | 有具体失控经历可展开：'暴饮暴食，买一堆零食吃，喝酒...' | 一句话感受可作为开场共鸣点：'很难减，没有正反馈就很容易放弃' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C018</t>
+          <t>C021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>重度脱轨</t>
+          <t>反复行动者</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -938,47 +1393,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13918155081</t>
+          <t>15865310577</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41岁以上</t>
+          <t>25-30岁</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
+          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>断断续续地在做，时有时无</t>
+          <t>是的，我现在正在做</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1-3年，3-5次</t>
+          <t>3年以上，6次以上（反复重启）</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>时不时会有（一周1-2次）</t>
+          <t>经常发生（一周好几次）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>当天放大——"既然已经破功了，</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>希望有人支持，但想私密地进行</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -988,14 +1443,64 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>从未停止，从未成功</t>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>H.其他（请填写）</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>核心目标用户。多次尝试说明动机强但缺乏持续支持，聊天切入点：过去哪些方法坚持最久、为什么停了。 | 高频失控（每周多次），可深入聊最近一次具体经历。 | 有当天放大模式，可聊'破功后当天'的典型心理过程。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C020</t>
+          <t>C022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,12 +1515,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cincin_mei</t>
+          <t>13808854400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1025,7 +1530,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
+          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1040,17 +1545,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>时不时会有（一周1-2次）</t>
+          <t>偶尔（一个月几次）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>几乎没影响——不太在意，很快就过去了</t>
+          <t>当天放大——"既然已经破功了，</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1060,19 +1565,84 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>很难减，没有正反馈就很容易放弃</t>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>没遇到</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>没遇到</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋C.智能硬件（体重秤、手环、手表等）┋D.私教或营养师（线上或线下）</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>应酬后放开饮食，原本打算第二天恢复节制，但往往会放纵更久时间导致前功尽弃</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>辟谷。社交需要。</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>反反复复</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>核心目标用户。多次尝试说明动机强但缺乏持续支持，聊天切入点：过去哪些方法坚持最久、为什么停了。 | 有当天放大模式，可聊'破功后当天'的典型心理过程。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 有具体失控经历可展开：'应酬后放开饮食，原本打算第二天恢复节制，但往往会放纵更久时间...' | 一句话感受可作为开场共鸣点：'反反复复' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C021</t>
+          <t>C025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>反复行动者</t>
+          <t>重度脱轨</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1082,12 +1652,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15865310577</t>
+          <t>18642950831</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1097,12 +1667,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
+          <t>目前不在工作（学生、全职家庭、待业等）</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>是的，我现在正在做</t>
+          <t>断断续续地在做，时有时无</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1112,39 +1682,99 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>经常发生（一周好几次）</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>当天放大——"既然已经破功了，今天就算了"，当天彻底放开</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>数百元</t>
+          <t>一千到三千（不含）</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>(空)</t>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16+8，很容易实现（早饭不吃）；一直在坚持，除非有社交或者高强度的一天</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>motivation不是非常坚定，确实身体很健康，理论上来说没有必要减肥；偶尔身材焦虑</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>高痛感用户，当前未行动。切入点：不要催促重启，而是了解当前状态和顾虑。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 一句话感受可作为开场共鸣点：'motivation不是非常坚定，确实身体很健康，理论上来说没有必要减肥；偶尔身材焦虑' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C022</t>
+          <t>C026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>反复行动者</t>
+          <t>重度脱轨</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1154,69 +1784,119 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13808854400</t>
+          <t>strawberryskyy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31-40岁</t>
+          <t>25-30岁</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
+          <t>目前不在工作（学生、全职家庭、待业等）</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>是的，我现在正在做</t>
+          <t>试过，但目前没有在坚持</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3年以上，6次以上（反复重启）</t>
+          <t>不到1年，3次以上</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>偶尔（一个月几次）</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>当天放大——"既然已经破功了，今天就算了"，当天彻底放开</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>希望有人支持，但想私密地进行</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>三千到一万</t>
+          <t>数百元</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>反反复复</t>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>B.运动/健身App（Keep等）</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>高痛感用户，当前未行动。切入点：不要催促重启，而是了解当前状态和顾虑。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C025</t>
+          <t>C030</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>重度脱轨</t>
+          <t>反复行动者</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1226,12 +1906,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18642950831</t>
+          <t>loverlancer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1241,12 +1921,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>目前不在工作（学生、全职家庭、待业等）</t>
+          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>断断续续地在做，时有时无</t>
+          <t>是的，我现在正在做</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1261,44 +1941,109 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>希望有人支持，但想私密地进行</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>一千到三千（不含）</t>
+          <t>三千到一万</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>motivation不是非常坚定，确实身体很健康，理论上来说没有必要减肥；偶尔身材焦虑</t>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>饿了点外卖</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>薄荷健康，因为有体脂秤</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>长期的好习惯才有用</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>核心目标用户。多次尝试说明动机强但缺乏持续支持，聊天切入点：过去哪些方法坚持最久、为什么停了。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 私教体验正面，可聊为什么有帮助、为什么没继续。 | 有具体失控经历可展开：'饿了点外卖...' | 一句话感受可作为开场共鸣点：'长期的好习惯才有用' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C026</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>重度脱轨</t>
+          <t>轻度脱轨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>strawberryskyy</t>
+          <t>19316572365</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1308,12 +2053,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25-30岁</t>
+          <t>18-24岁</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>目前不在工作（学生、全职家庭、待业等）</t>
+          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1323,22 +2068,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>不到1年，3次以上</t>
+          <t>不到1年，1-2次</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>时不时会有（一周1-2次）</t>
+          <t>偶尔（一个月几次）</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>希望有人支持，但想私密地进行</t>
+          <t>公开做，社交监督对自己有用</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1348,34 +2093,104 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>(空)</t>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>主要是自已会控制不住，偷偷吃很多东西</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>本来不应该喝奶茶，结果一天喝了两杯  很后悔喝</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>少吃晚饭  后来受不了饿</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>很难控制自已</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>痛感较低，社交偏好较高。需确认是否真的对私密 AI 教练有兴趣。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 有具体失控经历可展开：'本来不应该喝奶茶，结果一天喝了两杯  很后悔喝...' | 一句话感受可作为开场共鸣点：'很难控制自已'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C030</t>
+          <t>P031</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>反复行动者</t>
+          <t>重度脱轨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>loverlancer</t>
+          <t>13646639011</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1385,17 +2200,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>不太规律，经常有应酬、出差或临时安排打乱计划</t>
+          <t>目前不在工作（学生、全职家庭、待业等）</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>是的，我现在正在做</t>
+          <t>试过，但目前没有在坚持</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3年以上，6次以上（反复重启）</t>
+          <t>不到1年，3次以上</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1405,7 +2220,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1415,44 +2230,114 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>三千到一万</t>
+          <t>一千到三千（不含）</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>长期的好习惯才有用</t>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋D.私教或营养师（线上或线下）</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>因为过一段时间就坚持不住了</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>有一天晚上饿的睡不着没办法点了外卖吃了第二天胖了两斤过后想以后在饿也不能吃了</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>跑步锻炼刚开始有用后面就没什么用了就坚持不下去了</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>想减肥控制体重必须锻炼加节食</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>高痛感用户，当前未行动。切入点：不要催促重启，而是了解当前状态和顾虑。 | 有具体失控经历可展开：'有一天晚上饿的睡不着没办法点了外卖吃了第二天胖了两斤过后想以...' | 一句话感受可作为开场共鸣点：'想减肥控制体重必须锻炼加节食' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C037</t>
+          <t>P032</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>反复行动者</t>
+          <t>起步行动者</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hammer_estelle</t>
+          <t>19192104471</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31-40岁</t>
+          <t>25-30岁</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1467,22 +2352,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3年以上，6次以上（反复重启）</t>
+          <t>1-3年，1-2次</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>时不时会有（一周1-2次）</t>
+          <t>偶尔（一个月几次）</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>当天放大——"既然已经破功了，今天就算了"，当天彻底放开</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1492,19 +2377,89 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>在最开始，吃比练重要</t>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>几乎没影响</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋E.付费课程或训练营</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>运动量会有严格控制，饮食也会监督。</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>今年2月份朋友买车聚餐，明明打算随礼就行后面还是去参加了，当时想着要给朋友面子就去了，但吃完回来发现体重长了心情非常懊悔。</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>去健身房健身，持续了2年，有时候多吃了就想着去消耗热量。</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>坚持下去</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>刚起步，困难度较低。切入点：了解当前在用什么方法、遇到的第一个卡点是什么。 | 私教体验正面，可聊为什么有帮助、为什么没继续。 | 有具体失控经历可展开：'今年2月份朋友买车聚餐，明明打算随礼就行后面还是去参加了，当...' | 一句话感受可作为开场共鸣点：'坚持下去' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P033</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>重度脱轨</t>
+          <t>起步行动者</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1514,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>没有</t>
+          <t>13406608692</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1534,27 +2489,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>试过，但目前没有在坚持</t>
+          <t>是的，我现在正在做</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>不到1年，3次以上</t>
+          <t>1-3年，1-2次</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>经常发生（一周好几次）</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>和身边的人一起做</t>
+          <t>习惯自己默默做，不太需要别人参</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1564,19 +2519,89 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>比起极端的“快速瘦”，能长期坚持的、不折磨自己的方式，才是减脂的终点。</t>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>营养师的饮食搭配好多都是少吃、节食，不科学</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>周末在家休息，本打算不吃饭轻断食，但后来因为饿了就没忍住点了外卖，吃了之后又觉得很有罪恶感，懊恼了一会儿，晚上做了运动心里感觉好受了很多</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>keep，里面有很多训练教程</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>减肥是一辈子的事</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>刚起步，困难度较低。切入点：了解当前在用什么方法、遇到的第一个卡点是什么。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 有具体失控经历可展开：'周末在家休息，本打算不吃饭轻断食，但后来因为饿了就没忍住点了...' | 一句话感受可作为开场共鸣点：'减肥是一辈子的事'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>轻度脱轨</t>
+          <t>起步行动者</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1586,7 +2611,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19316572365</t>
+          <t>15920362507</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1596,7 +2621,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18-24岁</t>
+          <t>25-30岁</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1606,27 +2631,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>试过，但目前没有在坚持</t>
+          <t>是的，我现在正在做</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>不到1年，1-2次</t>
+          <t>1-3年，1-2次</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>偶尔（一个月几次）</t>
+          <t>时不时会有（一周1-2次）</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>公开做，社交监督对自己有用</t>
+          <t>希望有人支持，但想私密地进行</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1636,19 +2661,89 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>很难控制自已</t>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>试过，没什么用</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>没试过</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋C.智能硬件（体重秤、手环、手表等）┋F.减脂相关的自媒体内容（小红书、抖音博主等）</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>因为自己控制不住偷偷吃东西</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>吃烤肉，因为朋友聚会，事后比较后悔</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>练八段锦，时间不够</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>管住嘴迈开腿真的很难</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>刚起步，困难度较低。切入点：了解当前在用什么方法、遇到的第一个卡点是什么。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 没试过私教，可了解原因（费用？隐私？不知道找谁？）。 | 有具体失控经历可展开：'吃烤肉，因为朋友聚会，事后比较后悔...' | 一句话感受可作为开场共鸣点：'管住嘴迈开腿真的很难'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P031</t>
+          <t>P046</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>重度脱轨</t>
+          <t>起步行动者</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1658,32 +2753,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13646639011</t>
+          <t>131519900082</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-30岁</t>
+          <t>31-40岁</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>目前不在工作（学生、全职家庭、待业等）</t>
+          <t>节奏比较固定，大部分时间能自己安排（比如远程办公、自由职业、独立创作）</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>试过，但目前没有在坚持</t>
+          <t>是的，我现在正在做</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>不到1年，3次以上</t>
+          <t>不到1年，1-2次</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1693,7 +2788,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
+          <t>短暂懊恼——有点后悔，但第二天</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1708,367 +2803,77 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>想减肥控制体重必须锻炼加节食</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>P032</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>起步行动者</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>19192104471</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>25-30岁</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>是的，我现在正在做</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1-3年，1-2次</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>偶尔（一个月几次）</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>一千到三千（不含）</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>坚持下去</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P033</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>起步行动者</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>13406608692</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>31-40岁</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>是的，我现在正在做</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1-3年，1-2次</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>时不时会有（一周1-2次）</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>数百元</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>减肥是一辈子的事</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P034</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>起步行动者</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>好</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>41岁以上</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>节奏比较固定，大部分时间能自己安排（比如远程办公、自由职业、独立创作）</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>是的，我现在正在做</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>不到1年，1-2次</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>偶尔（一个月几次）</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>难以恢复——会低落一阵子，或者中断后很难重新捡起来</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>习惯自己默默做，不太需要别人参与</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>没花过钱</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>难</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P035</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>起步行动者</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>15920362507</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>25-30岁</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>节奏基本规律，但工作中经常需要开会、协作或面对客户</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>是的，我现在正在做</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1-3年，1-2次</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>时不时会有（一周1-2次）</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>希望有人支持，但想私密地进行</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>数百元</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>管住嘴迈开腿真的很难</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P046</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>起步行动者</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>131519900082</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>31-40岁</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>节奏比较固定，大部分时间能自己安排（比如远程办公、自由职业、独立创作）</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>是的，我现在正在做</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>不到1年，1-2次</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>时不时会有（一周1-2次）</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>短暂懊恼——有点后悔，但第二天基本能调整回来</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>希望有人支持，但想私密地进行</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>一千到三千（不含）</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>彻底打乱节奏</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>有些影响，能调整回来</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>影响很大，基本失控</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>试过，确实有帮助</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>试过，有一点用</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>A.记录饮食的App（薄荷健康等）┋B.运动/健身App（Keep等）┋C.智能硬件（体重秤、手环、手表等）┋D.私教或营养师（线上或线下）┋F.减脂相关的自媒体内容（小红书、抖音博主等）┋G.社群或打卡活动（微信群等）</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>效果很好，科学健康的饮食有助于减重</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>又一次加班到很晚，非常饿，没控制住自己的饮食，导致体重上升，后来我告诉行ˆ_ˆ自己也不管什么时候都要控制好自己</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>坚持跑步，坚持了半年，有利于提高身体素质</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>坚持坚持再坚持，就是胜利</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>刚起步，困难度较低。切入点：了解当前在用什么方法、遇到的第一个卡点是什么。 | 工作压力是主要干扰源，可从工作节奏切入。 | 情绪波动影响大，可探讨情绪与饮食的关联。 | 私教体验正面，可聊为什么有帮助、为什么没继续。 | 有具体失控经历可展开：'又一次加班到很晚，非常饿，没控制住自己的饮食，导致体重上升，...' | 一句话感受可作为开场共鸣点：'坚持坚持再坚持，就是胜利' | 高花费用户，已有付费习惯，可探讨过去花在哪、效果如何。</t>
         </is>
       </c>
     </row>
